--- a/demo/(incrementality)260127_tiktok_multicell_cvr_lift.xlsx
+++ b/demo/(incrementality)260127_tiktok_multicell_cvr_lift.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://twdc-my.sharepoint.com/personal/shirley_deng_disney_com/Documents/Documents/winning_prob/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://twdc-my.sharepoint.com/personal/shirley_deng_disney_com/Documents/Documents/winning_prob/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="8_{904D1800-88DA-A24D-B962-31B32AD975CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5010B43-56A2-F047-A386-899E43A67B30}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{904D1800-88DA-A24D-B962-31B32AD975CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF5FB5DB-D67F-4B43-AFAB-B73A8E8C7AF4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19780" xr2:uid="{2B257662-BBB0-7E4F-AE21-5DF4D2EB5C7F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19780" xr2:uid="{2B257662-BBB0-7E4F-AE21-5DF4D2EB5C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -105,8 +105,8 @@
   <numFmts count="4">
     <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -213,7 +213,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -254,16 +254,16 @@
     <xf numFmtId="3" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -272,6 +272,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -289,10 +290,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -617,6 +614,7 @@
   <cols>
     <col min="1" max="2" width="22.33203125" customWidth="1"/>
     <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -812,9 +810,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="3"/>
-      <c r="N5" s="4"/>
+      <c r="J5" s="28"/>
       <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
